--- a/data/raw/vannmiljo/VM_Activties_MGR_Comments.xlsx
+++ b/data/raw/vannmiljo/VM_Activties_MGR_Comments.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://niva365-my.sharepoint.com/personal/sam_welch_niva_no/Documents/Documents/02 - Projects/EXPECT AEP/EXPECT_AEP_R_Project/data/raw/vannmiljo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAW\Local Documents\Vm2eData\data\raw\vannmiljo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{AEDB6E49-01F4-4C7A-8E3F-56B63278B47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2ACFC8C-C0EA-4E00-A7DD-D5D231D56BF6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBFB669-BC9A-435D-AAC9-71683CEB927E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2976" yWindow="2988" windowWidth="21996" windowHeight="11676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26100" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aktivitet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Aktivitet!$A$1:$E$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Aktivitet!$A$1:$G$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="282">
   <si>
     <t>ActivityID</t>
   </si>
@@ -811,6 +811,120 @@
   </si>
   <si>
     <t>André Staalstrøm</t>
+  </si>
+  <si>
+    <t>Relevant to Arctic Case Study</t>
+  </si>
+  <si>
+    <t>Ecology</t>
+  </si>
+  <si>
+    <t>Likely to be a mixed bag.</t>
+  </si>
+  <si>
+    <t>Presumably not a lot of pollution data?</t>
+  </si>
+  <si>
+    <t>Unlikely to have much pollution data</t>
+  </si>
+  <si>
+    <t>No pollution</t>
+  </si>
+  <si>
+    <t>Relevant data, but old.</t>
+  </si>
+  <si>
+    <t>Likely relevant, but may not be marine.</t>
+  </si>
+  <si>
+    <t>Non-marine.</t>
+  </si>
+  <si>
+    <t>Non-marine, non chemical.</t>
+  </si>
+  <si>
+    <t>Not marine</t>
+  </si>
+  <si>
+    <t>May be marine but unlikely to be an important source of data</t>
+  </si>
+  <si>
+    <t>Very old.</t>
+  </si>
+  <si>
+    <t>Likely little marine.</t>
+  </si>
+  <si>
+    <t>No marine.</t>
+  </si>
+  <si>
+    <t>Presumably highly relevant.</t>
+  </si>
+  <si>
+    <t>May be some marine?</t>
+  </si>
+  <si>
+    <t>Not pollution</t>
+  </si>
+  <si>
+    <t>Probably not marine?</t>
+  </si>
+  <si>
+    <t>largely marine?</t>
+  </si>
+  <si>
+    <t>Unclear.</t>
+  </si>
+  <si>
+    <t>Potentially highly relevant</t>
+  </si>
+  <si>
+    <t>Highly relevant.</t>
+  </si>
+  <si>
+    <t>Highly relevant</t>
+  </si>
+  <si>
+    <t>Microplastics out of scope</t>
+  </si>
+  <si>
+    <t>Probably out of scope</t>
+  </si>
+  <si>
+    <t>Marine but not arctic.</t>
+  </si>
+  <si>
+    <t>Relevant, but sites may be a long way from other sources</t>
+  </si>
+  <si>
+    <t>Mixed bag.</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Unclear. New pollutants may lack sufficient data for mixtures.</t>
+  </si>
+  <si>
+    <t>Not environmental</t>
+  </si>
+  <si>
+    <t>Unclear</t>
+  </si>
+  <si>
+    <t>Unclear, old.</t>
+  </si>
+  <si>
+    <t>Not ecotox</t>
+  </si>
+  <si>
+    <t>Not Arctic</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>May be relevant, but old.</t>
   </si>
 </sst>
 </file>
@@ -1212,18 +1326,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E71"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G71"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="1"/>
-    <col min="2" max="2" width="47.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="96.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38.69921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.3984375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="8.75" style="1"/>
+    <col min="2" max="2" width="47.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="96.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1239,805 +1355,1195 @@
       <c r="E1" s="1" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2" s="1">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F3" s="1">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F9" s="1">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F12" s="1">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="109.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="78" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="78" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="78" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="78" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="109.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="78" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="78" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="78" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="78" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>193</v>
       </c>
@@ -2050,8 +2556,14 @@
       <c r="E66" s="1" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>196</v>
       </c>
@@ -2064,63 +2576,98 @@
       <c r="E67" s="1" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+        <v>207</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>243</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E71" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G71" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G71">
+      <sortCondition descending="1" ref="F1:F71"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C12 A18:C71 A17:B17 A14:C14 A13 C13 A16:C16 A15 C15" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1" numberStoredAsText="1"/>
   </ignoredErrors>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>